--- a/Fiche éval DF 3e.xlsx
+++ b/Fiche éval DF 3e.xlsx
@@ -110,9 +110,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="0" formatCode="General"/>
-    <numFmt numFmtId="59" formatCode="0.0%"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -126,12 +125,12 @@
       <name val="Helvetica Neue"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="15"/>
       <color indexed="8"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="15"/>
+      <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
     </font>
@@ -189,7 +188,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -377,72 +376,186 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="14"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="14"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="14"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="14"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="14"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="14"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="14"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="14"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="14"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="5" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="6" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="2" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="59" fontId="5" fillId="2" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="2" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -466,6 +579,7 @@
       <rgbColor rgb="fff6c48d"/>
       <rgbColor rgb="ffffdf7f"/>
       <rgbColor rgb="ffb7d6a3"/>
+      <rgbColor rgb="ffaaaaaa"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -482,10 +596,10 @@
         <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="5E5E5E"/>
+        <a:srgbClr val="A7A7A7"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="D5D5D5"/>
+        <a:srgbClr val="535353"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="00A2FF"/>
@@ -662,11 +776,14 @@
     <a:spDef>
       <a:spPr>
         <a:solidFill>
-          <a:srgbClr val="000000"/>
+          <a:srgbClr val="FFFFFF"/>
         </a:solidFill>
-        <a:ln w="12700" cap="flat">
-          <a:noFill/>
-          <a:miter lim="400000"/>
+        <a:ln w="25400" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
         </a:ln>
         <a:effectLst/>
         <a:sp3d/>
@@ -675,33 +792,33 @@
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
-        <a:defPPr marL="0" marR="0" indent="0" algn="ctr" defTabSz="584200" rtl="0" fontAlgn="auto" latinLnBrk="0" hangingPunct="0">
-          <a:lnSpc>
-            <a:spcPct val="100000"/>
-          </a:lnSpc>
-          <a:spcBef>
-            <a:spcPts val="0"/>
-          </a:spcBef>
-          <a:spcAft>
-            <a:spcPts val="0"/>
-          </a:spcAft>
-          <a:buClrTx/>
-          <a:buSzTx/>
-          <a:buFontTx/>
-          <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1200" u="none" kumimoji="0" normalizeH="0">
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:solidFill>
-              <a:srgbClr val="FFFFFF"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:uFillTx/>
-            <a:latin typeface="Helvetica Neue Medium"/>
-            <a:ea typeface="Helvetica Neue Medium"/>
-            <a:cs typeface="Helvetica Neue Medium"/>
-            <a:sym typeface="Helvetica Neue Medium"/>
+        <a:defPPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="0" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -940,12 +1057,12 @@
     <a:lnDef>
       <a:spPr>
         <a:noFill/>
-        <a:ln w="12700" cap="flat">
+        <a:ln w="25400" cap="flat">
           <a:solidFill>
-            <a:srgbClr val="000000"/>
+            <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="400000"/>
+          <a:round/>
         </a:ln>
         <a:effectLst/>
         <a:sp3d/>
@@ -1226,7 +1343,7 @@
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
-        <a:defPPr marL="0" marR="0" indent="0" algn="l" defTabSz="457200" rtl="0" fontAlgn="auto" latinLnBrk="0" hangingPunct="0">
+        <a:defPPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="0" hangingPunct="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -1494,7 +1611,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="15.4" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="5" width="31.8516" style="1" customWidth="1"/>
@@ -1539,7 +1656,7 @@
         <v>10</v>
       </c>
       <c r="F2" s="11">
-        <v>0.25</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" ht="67.8" customHeight="1">
@@ -1559,7 +1676,7 @@
         <v>14</v>
       </c>
       <c r="F3" s="16">
-        <v>0.2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" ht="67.8" customHeight="1">
@@ -1579,7 +1696,7 @@
         <v>19</v>
       </c>
       <c r="F4" s="16">
-        <v>0.2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" ht="104.55" customHeight="1">
@@ -1599,7 +1716,7 @@
         <v>24</v>
       </c>
       <c r="F5" s="16">
-        <v>0.2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" ht="77.8" customHeight="1">
@@ -1619,8 +1736,40 @@
         <v>29</v>
       </c>
       <c r="F6" s="19">
-        <v>0.15</v>
-      </c>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" ht="14.7" customHeight="1">
+      <c r="A7" s="20"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="22"/>
+    </row>
+    <row r="8" ht="14.7" customHeight="1">
+      <c r="A8" s="23"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="25"/>
+    </row>
+    <row r="9" ht="14.7" customHeight="1">
+      <c r="A9" s="23"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="25"/>
+    </row>
+    <row r="10" ht="14.7" customHeight="1">
+      <c r="A10" s="26"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="28"/>
     </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.277778" footer="0.277778"/>

--- a/Fiche éval DF 3e.xlsx
+++ b/Fiche éval DF 3e.xlsx
@@ -64,16 +64,16 @@
     <t>Adapter l’intensité de son engagement physique à ses possibilités pour ne pas se mettre en danger</t>
   </si>
   <si>
-    <t xml:space="preserve">L’intensité moyenne des courses est inférieure à 90% </t>
-  </si>
-  <si>
-    <t>L’intensité moyenne des courses est comprise entre 90 et 94%</t>
-  </si>
-  <si>
-    <t>L’intensité moyenne des courses est comprise entre 95 et 99%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L’intensité moyenne des course est supérieur ou égal à 100%. L’élève court avec fluidité, régulièrement à la même vitesse tout au long de la course. </t>
+    <t xml:space="preserve">L’intensité moyenne des courses est inférieure à 75% </t>
+  </si>
+  <si>
+    <t>L’intensité moyenne des courses est comprise entre 75% et 85%</t>
+  </si>
+  <si>
+    <t>L’intensité moyenne des courses est comprise entre 85% et 91%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’intensité moyenne des course est supérieur ou égal à 92%. L’élève court avec fluidité, régulièrement à la même vitesse tout au long de la course. </t>
   </si>
   <si>
     <t>Prendre et assumer des responsabilités au sein d’un collectif pour réaliser un projet ou remplir un contrat</t>
